--- a/Shared/XLS/Projectile.xlsx
+++ b/Shared/XLS/Projectile.xlsx
@@ -19,7 +19,7 @@
     <author>양대용</author>
   </authors>
   <commentList>
-    <comment ref="J2" authorId="0">
+    <comment ref="E2" authorId="0">
       <text>
         <r>
           <rPr>
@@ -251,7 +251,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
   <si>
     <t>!ID</t>
   </si>
@@ -276,26 +276,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Speed</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accel</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxSpeed</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HomingRate</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxDistance</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>ExplodeRadius</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -321,6 +301,29 @@
   <si>
     <t>Pierce</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PJT_CrossBow_Bolt</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_CrossBow_Attack_Damage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefab_Projectile_CrossBow_Bolt</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PJT_Monster_Arrow</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefab_Projectile_Monster_Arrow</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_Monster_RangeAttack_Damage</t>
   </si>
 </sst>
 </file>
@@ -762,7 +765,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -770,30 +773,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T9"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.125" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.625" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.375" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.625" style="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.625" style="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.875" style="10" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18" style="10" customWidth="1"/>
-    <col min="13" max="13" width="9" style="10"/>
+    <col min="2" max="2" width="18" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.625" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.625" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.875" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18" style="10" customWidth="1"/>
+    <col min="8" max="8" width="9" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C1" s="8"/>
       <c r="D1" s="8"/>
@@ -801,20 +799,15 @@
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
       <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="4"/>
       <c r="B2" s="3" t="s">
         <v>0</v>
@@ -823,162 +816,116 @@
         <v>5</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="M2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="3" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2"/>
-      <c r="T3" s="2"/>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B4" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="9">
+        <v>1</v>
+      </c>
       <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
+      <c r="F4" s="9" t="s">
+        <v>14</v>
+      </c>
       <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>17</v>
+      </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
+      <c r="F5" s="9" t="s">
+        <v>18</v>
+      </c>
       <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
       <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
